--- a/cet4/result/20_科技女神_学霸的商业传奇/20_科技女神_学霸的商业传奇_学习版.xlsx
+++ b/cet4/result/20_科技女神_学霸的商业传奇/20_科技女神_学霸的商业传奇_学习版.xlsx
@@ -397,745 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sunshine</v>
       </c>
       <c r="B2" t="str">
-        <v>sunshine</v>
+        <v>/ˈsʌnʃaɪn/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>阳光</v>
       </c>
-      <c r="D2" t="str">
-        <v>sunshine(阳光)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>cottage</v>
       </c>
       <c r="B3" t="str">
-        <v>cottage</v>
+        <v>/ˈkɑːtɪdʒ/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>小屋</v>
       </c>
-      <c r="D3" t="str">
-        <v>cottage(小屋)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>Asian</v>
       </c>
       <c r="B4" t="str">
-        <v>Asian</v>
+        <v>/ˈeɪʒn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>亚洲的</v>
       </c>
-      <c r="D4" t="str">
-        <v>Asian(亚洲的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>nationality</v>
       </c>
       <c r="B5" t="str">
-        <v>nationality</v>
+        <v>/ˌnæʃəˈnæləti/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>国籍</v>
       </c>
-      <c r="D5" t="str">
-        <v>nationality(国籍)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>reason</v>
       </c>
       <c r="B6" t="str">
-        <v>reason</v>
+        <v>/ˈriːzn/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>理由</v>
       </c>
-      <c r="D6" t="str">
-        <v>reason(理由)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>king</v>
       </c>
       <c r="B7" t="str">
-        <v>king</v>
+        <v>/kɪŋ/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>国王</v>
       </c>
-      <c r="D7" t="str">
-        <v>king(国王)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>favourite</v>
       </c>
       <c r="B8" t="str">
-        <v>favourite</v>
+        <v>/ˈfeɪvərɪt/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>特别受喜爱的</v>
       </c>
-      <c r="D8" t="str">
-        <v>favourite(特别受喜爱的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>delicate</v>
       </c>
       <c r="B9" t="str">
-        <v>delicate</v>
+        <v>/ˈdelɪkət/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>微妙的</v>
       </c>
-      <c r="D9" t="str">
-        <v>delicate(微妙的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>convention</v>
       </c>
       <c r="B10" t="str">
-        <v>convention</v>
+        <v>/kənˈvenʃn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>大会</v>
       </c>
-      <c r="D10" t="str">
-        <v>convention(大会)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>unique</v>
       </c>
       <c r="B11" t="str">
-        <v>unique</v>
+        <v>/juˈniːk/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>独特的</v>
       </c>
-      <c r="D11" t="str">
-        <v>unique(独特的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>user</v>
       </c>
       <c r="B12" t="str">
-        <v>user</v>
+        <v>/ˈjuːzər/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>用户</v>
       </c>
-      <c r="D12" t="str">
-        <v>user(用户)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>dozen</v>
       </c>
       <c r="B13" t="str">
-        <v>dozen</v>
+        <v>/ˈdʌzn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>十二个</v>
       </c>
-      <c r="D13" t="str">
-        <v>dozen(十二个)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>wallet</v>
       </c>
       <c r="B14" t="str">
-        <v>wallet</v>
+        <v>/ˈwɑːlɪt/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>钱包</v>
       </c>
-      <c r="D14" t="str">
-        <v>wallet(钱包)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>technique</v>
       </c>
       <c r="B15" t="str">
-        <v>technique</v>
+        <v>/tekˈniːk/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>技巧</v>
       </c>
-      <c r="D15" t="str">
-        <v>technique(技巧)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>seek</v>
       </c>
       <c r="B16" t="str">
-        <v>seek</v>
+        <v>/siːk/</v>
       </c>
       <c r="C16" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>寻求</v>
       </c>
-      <c r="D16" t="str">
-        <v>seek(寻求)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>tired</v>
       </c>
       <c r="B17" t="str">
-        <v>tired</v>
+        <v>/ˈtaɪərd/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>疲倦的</v>
       </c>
-      <c r="D17" t="str">
-        <v>tired(疲倦的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>succession</v>
       </c>
       <c r="B18" t="str">
-        <v>succession</v>
+        <v>/səkˈseʃn/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>连续</v>
       </c>
-      <c r="D18" t="str">
-        <v>succession(连续)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>hawk</v>
       </c>
       <c r="B19" t="str">
-        <v>hawk</v>
+        <v>/hɔːk/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D19" t="str">
         <v>鹰</v>
       </c>
-      <c r="D19" t="str">
-        <v>hawk(鹰)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>literature</v>
       </c>
       <c r="B20" t="str">
-        <v>literature</v>
+        <v>/ˈlɪtrətʃər; ˈlɪtrətʃʊr/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>文献</v>
       </c>
-      <c r="D20" t="str">
-        <v>literature(文献)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>investigate</v>
       </c>
       <c r="B21" t="str">
-        <v>investigate</v>
+        <v>/ɪnˈvestɪɡeɪt/</v>
       </c>
       <c r="C21" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D21" t="str">
         <v>调查</v>
       </c>
-      <c r="D21" t="str">
-        <v>investigate(调查)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>glory</v>
       </c>
       <c r="B22" t="str">
-        <v>glory</v>
+        <v>/ˈɡlɔːri/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>光荣</v>
       </c>
-      <c r="D22" t="str">
-        <v>glory(光荣)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>leadership</v>
       </c>
       <c r="B23" t="str">
-        <v>leadership</v>
+        <v>/ˈliːdərʃɪp/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>领导能力</v>
       </c>
-      <c r="D23" t="str">
-        <v>leadership(领导能力)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>moderate</v>
       </c>
       <c r="B24" t="str">
-        <v>moderate</v>
+        <v>/ˈmɑːdərət/</v>
       </c>
       <c r="C24" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>稳健的</v>
       </c>
-      <c r="D24" t="str">
-        <v>moderate(稳健的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>school</v>
       </c>
       <c r="B25" t="str">
-        <v>school</v>
+        <v>/skuːl/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D25" t="str">
         <v>学校</v>
       </c>
-      <c r="D25" t="str">
-        <v>school(学校)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>accident</v>
       </c>
       <c r="B26" t="str">
-        <v>accident</v>
+        <v>/ˈæksɪdənt/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>事故</v>
       </c>
-      <c r="D26" t="str">
-        <v>accident(事故)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>glare</v>
       </c>
       <c r="B27" t="str">
-        <v>glare</v>
+        <v>/ɡler/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>怒视</v>
       </c>
-      <c r="D27" t="str">
-        <v>glare(怒视)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>involve</v>
       </c>
       <c r="B28" t="str">
-        <v>involve</v>
+        <v>/ɪnˈvɑːlv/</v>
       </c>
       <c r="C28" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D28" t="str">
         <v>包含</v>
       </c>
-      <c r="D28" t="str">
-        <v>involve(包含)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>confusion</v>
       </c>
       <c r="B29" t="str">
-        <v>confusion</v>
+        <v>/kənˈfjuːʒn/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>混乱</v>
       </c>
-      <c r="D29" t="str">
-        <v>confusion(混乱)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>resistant</v>
       </c>
       <c r="B30" t="str">
-        <v>resistant</v>
+        <v>/rɪˈzɪstənt/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D30" t="str">
         <v>抵抗的</v>
       </c>
-      <c r="D30" t="str">
-        <v>resistant(抵抗的)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>repent</v>
       </c>
       <c r="B31" t="str">
-        <v>repent</v>
+        <v>/rɪˈpent/</v>
       </c>
       <c r="C31" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D31" t="str">
         <v>后悔</v>
       </c>
-      <c r="D31" t="str">
-        <v>repent(后悔)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>qualify</v>
       </c>
       <c r="B32" t="str">
-        <v>qualify</v>
+        <v>/ˈkwɑːlɪfaɪ/</v>
       </c>
       <c r="C32" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>使具有资格</v>
       </c>
-      <c r="D32" t="str">
-        <v>qualify(使具有资格)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>recommend</v>
       </c>
       <c r="B33" t="str">
-        <v>recommend</v>
+        <v>/ˌrekəˈmend/</v>
       </c>
       <c r="C33" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D33" t="str">
         <v>推荐</v>
       </c>
-      <c r="D33" t="str">
-        <v>recommend(推荐)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>widely</v>
       </c>
       <c r="B34" t="str">
-        <v>widely</v>
+        <v>/ˈwaɪdli/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D34" t="str">
         <v>广泛地</v>
       </c>
-      <c r="D34" t="str">
-        <v>widely(广泛地)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>graceful</v>
       </c>
       <c r="B35" t="str">
-        <v>graceful</v>
+        <v>/ˈɡreɪsfl/</v>
       </c>
       <c r="C35" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D35" t="str">
         <v>优雅的</v>
       </c>
-      <c r="D35" t="str">
-        <v>graceful(优雅的)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>mother</v>
       </c>
       <c r="B36" t="str">
-        <v>mother</v>
+        <v>/ˈmʌðər/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>母亲</v>
       </c>
-      <c r="D36" t="str">
-        <v>mother(母亲)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>husband</v>
       </c>
       <c r="B37" t="str">
-        <v>husband</v>
+        <v>/ˈhʌzbənd/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D37" t="str">
         <v>丈夫</v>
       </c>
-      <c r="D37" t="str">
-        <v>husband(丈夫)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>facility</v>
       </c>
       <c r="B38" t="str">
-        <v>facility</v>
+        <v>/fəˈsɪləti/</v>
       </c>
       <c r="C38" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>设施</v>
       </c>
-      <c r="D38" t="str">
-        <v>facility(设施)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>motive</v>
       </c>
       <c r="B39" t="str">
-        <v>Asian</v>
+        <v>/ˈmoʊtɪv/</v>
       </c>
       <c r="C39" t="str">
-        <v>亚洲的</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>Asian(亚洲的)📢</v>
+        <v>动机</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>friction</v>
       </c>
       <c r="B40" t="str">
-        <v>motive</v>
+        <v>/ˈfrɪkʃn/</v>
       </c>
       <c r="C40" t="str">
-        <v>动机</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>motive(动机)📢</v>
+        <v>摩擦</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>remind</v>
       </c>
       <c r="B41" t="str">
-        <v>friction</v>
+        <v>/rɪˈmaɪnd/</v>
       </c>
       <c r="C41" t="str">
-        <v>摩擦</v>
+        <v>vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>friction(摩擦)📢</v>
+        <v>提醒</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>along</v>
       </c>
       <c r="B42" t="str">
-        <v>remind</v>
+        <v>/əˈlɔːŋ/</v>
       </c>
       <c r="C42" t="str">
-        <v>提醒</v>
+        <v>v./adv./prep.</v>
       </c>
       <c r="D42" t="str">
-        <v>remind(提醒)📢</v>
+        <v>沿着</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>seem</v>
       </c>
       <c r="B43" t="str">
-        <v>along</v>
+        <v>/siːm/</v>
       </c>
       <c r="C43" t="str">
-        <v>沿着</v>
+        <v>n./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>along(沿着)📢</v>
+        <v>似乎</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>heaven</v>
       </c>
       <c r="B44" t="str">
-        <v>seem</v>
+        <v>/ˈhevn/</v>
       </c>
       <c r="C44" t="str">
-        <v>似乎</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>seem(似乎)📢</v>
+        <v>天堂</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>score</v>
       </c>
       <c r="B45" t="str">
-        <v>heaven</v>
+        <v>/skɔːr/</v>
       </c>
       <c r="C45" t="str">
-        <v>天堂</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>heaven(天堂)📢</v>
+        <v>分数</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>naturally</v>
       </c>
       <c r="B46" t="str">
-        <v>score</v>
+        <v>/ˈnætʃrəli/</v>
       </c>
       <c r="C46" t="str">
-        <v>分数</v>
+        <v>v./adv.</v>
       </c>
       <c r="D46" t="str">
-        <v>score(分数)📢</v>
+        <v>自然地</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>regardless</v>
       </c>
       <c r="B47" t="str">
-        <v>sunshine</v>
+        <v>/rɪˈɡɑːrdləs/</v>
       </c>
       <c r="C47" t="str">
-        <v>阳光</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D47" t="str">
-        <v>sunshine(阳光)📢</v>
+        <v>不管</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>beam</v>
       </c>
       <c r="B48" t="str">
-        <v>naturally</v>
+        <v>/biːm/</v>
       </c>
       <c r="C48" t="str">
-        <v>自然地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>naturally(自然地)📢</v>
+        <v>光线</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>tomato</v>
       </c>
       <c r="B49" t="str">
-        <v>regardless</v>
+        <v>/təˈmeɪtoʊ/</v>
       </c>
       <c r="C49" t="str">
-        <v>不管</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>regardless(不管)📢</v>
+        <v>番茄</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>edge</v>
       </c>
       <c r="B50" t="str">
-        <v>beam</v>
+        <v>/edʒ/</v>
       </c>
       <c r="C50" t="str">
-        <v>光线</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>beam(光线)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>tomato</v>
-      </c>
-      <c r="C51" t="str">
-        <v>番茄</v>
-      </c>
-      <c r="D51" t="str">
-        <v>tomato(番茄)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>edge</v>
-      </c>
-      <c r="C52" t="str">
         <v>边缘</v>
-      </c>
-      <c r="D52" t="str">
-        <v>edge(边缘)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>